--- a/GRAMMAR/13_24_12.xlsx
+++ b/GRAMMAR/13_24_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAEF638-673A-4F70-AD11-2D6CCE6AF61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143B733F-223E-4CFC-B862-43A59846B2AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20355" yWindow="1260" windowWidth="27840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="27840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -111,10 +111,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>一不小心就…;一不留神</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>まず～だろう</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -412,6 +408,10 @@
   </si>
   <si>
     <t>同"てあげる"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一不小心就…;一不留神;忍不住…</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>7</v>
@@ -957,10 +957,10 @@
         <v>0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -970,10 +970,10 @@
         <v>0</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -983,10 +983,10 @@
         <v>0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -996,14 +996,14 @@
         <v>0</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
@@ -1011,10 +1011,10 @@
         <v>0</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -1024,10 +1024,10 @@
         <v>0</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -1037,10 +1037,10 @@
         <v>0</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -1050,10 +1050,10 @@
         <v>0</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -1063,10 +1063,10 @@
         <v>0</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -1076,10 +1076,10 @@
         <v>0</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -1089,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -1102,10 +1102,10 @@
         <v>0</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -1115,10 +1115,10 @@
         <v>0</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -1128,13 +1128,13 @@
         <v>0</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="E25" s="2"/>
     </row>
@@ -1143,10 +1143,10 @@
         <v>0</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -1169,10 +1169,10 @@
         <v>0</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -1182,14 +1182,14 @@
         <v>0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
@@ -1197,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -1210,10 +1210,10 @@
         <v>0</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -1236,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
@@ -1262,10 +1262,10 @@
         <v>0</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -1288,10 +1288,10 @@
         <v>0</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -1301,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -1314,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -1327,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
@@ -1340,10 +1340,10 @@
         <v>0</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
@@ -1366,10 +1366,10 @@
         <v>0</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
@@ -1392,10 +1392,10 @@
         <v>0</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
